--- a/Output/PowerPoint_Figures/Fig_8/Fig_8c_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_8/Fig_8c_data.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,39 +418,39 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Std</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Plot_Type</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\stage2_results_5fold.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/stage2_results_5fold.csv</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -493,7 +481,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,7 +497,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\stage2_results_5fold.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/stage2_results_5fold.csv</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -524,7 +512,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -540,7 +528,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\stage2_results_5fold.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/stage2_results_5fold.csv</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -555,7 +543,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -571,7 +559,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\stage2_results_5fold.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/stage2_results_5fold.csv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -600,54 +588,54 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>N_Folds</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>AUC</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>MCC</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>20</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -680,12 +668,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\stage2_results_5fold.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/stage2_results_5fold.csv</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>21</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -718,12 +706,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\stage2_results_5fold.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/stage2_results_5fold.csv</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>22</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -756,12 +744,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\stage2_results_5fold.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/stage2_results_5fold.csv</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>23</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -794,12 +782,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\stage2_results_5fold.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/stage2_results_5fold.csv</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>24</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -832,12 +820,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\stage2_results_5fold.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/stage2_results_5fold.csv</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>25</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -870,12 +858,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\stage2_results_5fold.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/stage2_results_5fold.csv</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>26</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -908,12 +896,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\stage2_results_5fold.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/stage2_results_5fold.csv</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>27</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -946,12 +934,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\stage2_results_5fold.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/stage2_results_5fold.csv</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>28</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -984,12 +972,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\stage2_results_5fold.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/stage2_results_5fold.csv</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>29</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1022,7 +1010,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Performance_Metrics\stage2_results_5fold.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Performance_Metrics/stage2_results_5fold.csv</t>
         </is>
       </c>
     </row>
